--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TF57F8231-000002</x:t>
+    <x:t>TF772282D-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TF772282D-000002</x:t>
+    <x:t>TD83C861E-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TD83C861E-000002</x:t>
+    <x:t>T6484361B-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T6484361B-000002</x:t>
+    <x:t>T35B69F32-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T35B69F32-000002</x:t>
+    <x:t>T5A0C5991-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T5A0C5991-000002</x:t>
+    <x:t>T7A4725B2-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T7A4725B2-000002</x:t>
+    <x:t>TAF31274D-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TAF31274D-000002</x:t>
+    <x:t>TEDE1F137-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TEDE1F137-000002</x:t>
+    <x:t>T7B7BFFE7-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>T7B7BFFE7-000002</x:t>
+    <x:t>TB1A1E991-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>

--- a/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
+++ b/src/test/fixtures/forms-responses-http/export-state-pendingapproval-d2.xlsx
@@ -42,7 +42,7 @@
     <x:t>date</x:t>
   </x:si>
   <x:si>
-    <x:t>TB1A1E991-000002</x:t>
+    <x:t>T9CA46238-000002</x:t>
   </x:si>
   <x:si>
     <x:t>Sin información</x:t>
